--- a/tools/importer/reports/import-insurance-hub.report.xlsx
+++ b/tools/importer/reports/import-insurance-hub.report.xlsx
@@ -52,7 +52,7 @@
     <t>insurance-hub</t>
   </si>
   <si>
-    <t>2026-07-09T14:45:43.784Z</t>
+    <t>2026-07-09T16:31:59.124Z</t>
   </si>
   <si>
     <t>Types of Insurance Coverage | State Farm® - State Farm®</t>
@@ -73,7 +73,7 @@
     <t>insurance-product</t>
   </si>
   <si>
-    <t>2026-07-09T14:38:36.128Z</t>
+    <t>2026-07-09T14:45:53.991Z</t>
   </si>
   <si>
     <t>Car Insurance | Free Auto Insurance Quote</t>
@@ -85,13 +85,13 @@
     <t>insurance/homeowners.report.json</t>
   </si>
   <si>
-    <t>["hero-quote","columns-subnav","columns-subnav","columns-agent-cta","columns-agent-cta","columns-agent-cta","cards-checklist","accordion-faq","cards-article","columns-promo"]</t>
+    <t>["hero-quote","columns-subnav","columns-subnav","columns-agent-cta","columns-agent-cta","columns-agent-cta","cards-coverage","cards-checklist","accordion-faq","cards-article","cards-article","columns-promo"]</t>
   </si>
   <si>
     <t>insurance/homeowners</t>
   </si>
   <si>
-    <t>2026-07-09T14:38:44.204Z</t>
+    <t>2026-07-09T16:16:13.384Z</t>
   </si>
   <si>
     <t>Homeowners Insurance: Get a free quote today</t>

--- a/tools/importer/reports/import-insurance-hub.report.xlsx
+++ b/tools/importer/reports/import-insurance-hub.report.xlsx
@@ -52,7 +52,7 @@
     <t>insurance-hub</t>
   </si>
   <si>
-    <t>2026-07-09T16:31:59.124Z</t>
+    <t>2026-07-09T16:54:29.833Z</t>
   </si>
   <si>
     <t>Types of Insurance Coverage | State Farm® - State Farm®</t>
@@ -73,7 +73,7 @@
     <t>insurance-product</t>
   </si>
   <si>
-    <t>2026-07-09T14:45:53.991Z</t>
+    <t>2026-07-09T16:32:10.947Z</t>
   </si>
   <si>
     <t>Car Insurance | Free Auto Insurance Quote</t>
@@ -91,7 +91,7 @@
     <t>insurance/homeowners</t>
   </si>
   <si>
-    <t>2026-07-09T16:16:13.384Z</t>
+    <t>2026-07-09T16:32:20.743Z</t>
   </si>
   <si>
     <t>Homeowners Insurance: Get a free quote today</t>
